--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.tutorials/Tutorial 5 - Introduction to TBasic Tables/rules/Tutorial5 - Intro to TBasic Tables.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.tutorials/Tutorial 5 - Introduction to TBasic Tables/rules/Tutorial5 - Intro to TBasic Tables.xlsx
@@ -679,7 +679,7 @@
     <t>FUNCTION</t>
   </si>
   <si>
-    <t>i++</t>
+    <t>i += 1</t>
   </si>
   <si>
     <t>multiplier (1 .. n)</t>
